--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.3460910396299</v>
+        <v>7.20623979393986</v>
       </c>
       <c r="D2" t="n">
-        <v>9.702194993487899</v>
+        <v>1.576606686441784</v>
       </c>
       <c r="E2" t="n">
-        <v>5.104029944735935</v>
+        <v>0.8294048660195893</v>
       </c>
       <c r="F2" t="n">
-        <v>6.925797866338473</v>
+        <v>1.125442153280002</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.04513613809308</v>
+        <v>7.969834622440126</v>
       </c>
       <c r="D3" t="n">
-        <v>23.13255593115814</v>
+        <v>3.759040338813197</v>
       </c>
       <c r="E3" t="n">
-        <v>5.104029944735935</v>
+        <v>0.8294048660195893</v>
       </c>
       <c r="F3" t="n">
-        <v>6.925797866338473</v>
+        <v>1.125442153280002</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.85911312975482</v>
+        <v>8.102105883585159</v>
       </c>
       <c r="D4" t="n">
-        <v>25.60795503571324</v>
+        <v>4.161292693303402</v>
       </c>
       <c r="E4" t="n">
-        <v>5.104029944735935</v>
+        <v>0.8294048660195893</v>
       </c>
       <c r="F4" t="n">
-        <v>6.925797866338473</v>
+        <v>1.125442153280002</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.71474327774103</v>
+        <v>8.566145782632917</v>
       </c>
       <c r="D5" t="n">
-        <v>8.757112483670427</v>
+        <v>1.423030778596444</v>
       </c>
       <c r="E5" t="n">
-        <v>5.104029944735935</v>
+        <v>0.8294048660195893</v>
       </c>
       <c r="F5" t="n">
-        <v>6.925797866338473</v>
+        <v>1.125442153280002</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>59.83433401871139</v>
+        <v>9.723079278040601</v>
       </c>
       <c r="D6" t="n">
-        <v>19.77593520401008</v>
+        <v>3.213589470651637</v>
       </c>
       <c r="E6" t="n">
-        <v>5.104029944735935</v>
+        <v>0.8294048660195893</v>
       </c>
       <c r="F6" t="n">
-        <v>6.925797866338473</v>
+        <v>1.125442153280002</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
